--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OHIO_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OHIO_2019.xlsx
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="D11">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="12">
@@ -571,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="13">
@@ -2407,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="D114">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="115">
@@ -2515,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="121">
@@ -2569,7 +2569,7 @@
         <v>4</v>
       </c>
       <c r="D123">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="124">
@@ -2713,7 +2713,7 @@
         <v>4</v>
       </c>
       <c r="D131">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="132">
@@ -2731,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="D132">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="133">
@@ -2929,7 +2929,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="144">
@@ -3037,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="D149">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="150">
@@ -3271,7 +3271,7 @@
         <v>4</v>
       </c>
       <c r="D162">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="163">
@@ -3325,7 +3325,7 @@
         <v>4</v>
       </c>
       <c r="D165">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="166">
@@ -3775,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="D190">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="191">
@@ -3919,7 +3919,7 @@
         <v>4</v>
       </c>
       <c r="D198">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="199">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C199">
@@ -4135,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="D210">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="211">
@@ -4261,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="D217">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="218">
@@ -4549,7 +4549,7 @@
         <v>4</v>
       </c>
       <c r="D233">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="234">
@@ -5017,7 +5017,7 @@
         <v>4</v>
       </c>
       <c r="D259">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="260">
@@ -5071,7 +5071,7 @@
         <v>4</v>
       </c>
       <c r="D262">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="263">
@@ -5539,7 +5539,7 @@
         <v>4</v>
       </c>
       <c r="D288">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="289">
@@ -6511,7 +6511,7 @@
         <v>4</v>
       </c>
       <c r="D342">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="343">
@@ -6583,7 +6583,7 @@
         <v>4</v>
       </c>
       <c r="D346">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="347">
@@ -6637,7 +6637,7 @@
         <v>4</v>
       </c>
       <c r="D349">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="350">
@@ -7015,7 +7015,7 @@
         <v>4</v>
       </c>
       <c r="D370">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="371">
@@ -7519,7 +7519,7 @@
         <v>4</v>
       </c>
       <c r="D398">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="399">
@@ -7591,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="D402">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="403">
@@ -7645,7 +7645,7 @@
         <v>4</v>
       </c>
       <c r="D405">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="406">
@@ -7735,7 +7735,7 @@
         <v>4</v>
       </c>
       <c r="D410">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="411">
@@ -7879,7 +7879,7 @@
         <v>4</v>
       </c>
       <c r="D418">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="419">
@@ -8563,7 +8563,7 @@
         <v>4</v>
       </c>
       <c r="D456">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="457">
@@ -8833,7 +8833,7 @@
         <v>4</v>
       </c>
       <c r="D471">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="472">
@@ -8869,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="D473">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="474">
@@ -9373,7 +9373,7 @@
         <v>4</v>
       </c>
       <c r="D501">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="502">
@@ -9463,7 +9463,7 @@
         <v>4</v>
       </c>
       <c r="D506">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="507">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C519">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C520">
@@ -10057,7 +10057,7 @@
         <v>4</v>
       </c>
       <c r="D539">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="540">
@@ -10381,7 +10381,7 @@
         <v>4</v>
       </c>
       <c r="D557">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="558">
@@ -10507,7 +10507,7 @@
         <v>4</v>
       </c>
       <c r="D564">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="565">
@@ -10687,7 +10687,7 @@
         <v>4</v>
       </c>
       <c r="D574">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="575">
@@ -12001,7 +12001,7 @@
         <v>4</v>
       </c>
       <c r="D647">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="648">
@@ -12721,7 +12721,7 @@
         <v>4</v>
       </c>
       <c r="D687">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="688">
@@ -12937,7 +12937,7 @@
         <v>4</v>
       </c>
       <c r="D699">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="700">
@@ -13117,7 +13117,7 @@
         <v>4</v>
       </c>
       <c r="D709">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="710">
@@ -13549,7 +13549,7 @@
         <v>4</v>
       </c>
       <c r="D733">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="734">
@@ -13801,7 +13801,7 @@
         <v>4</v>
       </c>
       <c r="D747">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="748">
@@ -13927,7 +13927,7 @@
         <v>4</v>
       </c>
       <c r="D754">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="755">
@@ -14125,7 +14125,7 @@
         <v>4</v>
       </c>
       <c r="D765">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="766">
@@ -14503,7 +14503,7 @@
         <v>4</v>
       </c>
       <c r="D786">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="787">
@@ -14593,7 +14593,7 @@
         <v>4</v>
       </c>
       <c r="D791">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="792">
@@ -14611,7 +14611,7 @@
         <v>4</v>
       </c>
       <c r="D792">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="793">
@@ -14683,7 +14683,7 @@
         <v>4</v>
       </c>
       <c r="D796">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="797">
@@ -15025,7 +15025,7 @@
         <v>4</v>
       </c>
       <c r="D815">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="816">
@@ -15259,7 +15259,7 @@
         <v>4</v>
       </c>
       <c r="D828">
-        <v>0.0009720534629404617</v>
+        <v>0.0009720534629404616</v>
       </c>
     </row>
     <row r="829">
